--- a/education_surveys/016_sociology_student_feedback_survey--education_surveys.xlsx
+++ b/education_surveys/016_sociology_student_feedback_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>course_title</t>
+          <t>overall_impression</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your overall impression of the course?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide a short description of your experience in the course.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,64 +547,64 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>instructor_name</t>
+          <t>course_satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Instructor Name</t>
+          <t>How satisfied are you with the course?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>course_satisfaction</t>
+          <t>materials_provision</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How satisfied are you with the course?</t>
+          <t>Were you provided with enough resources and materials?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>course_satisfaction_why</t>
+          <t>course_structure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Why do you feel that way about the course?</t>
+          <t>How well was the course structured?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +616,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>teaching_effectiveness</t>
+          <t>course_rating</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The course helped me in developing my critical thinking and problem-solving skills.</t>
+          <t>How would you rate the course?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>course_materials</t>
+          <t>instructor_impression</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Were you provided with enough resources and materials?</t>
+          <t>How would you rate the instructor?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>course_structure</t>
+          <t>instructor_effectiveness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How well was the course structured?</t>
+          <t>How would you rate the instructor's teaching effectiveness?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +685,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>course_feedback</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Do you have any suggestions or comments?</t>
+          <t>Do you have any comments or suggestions?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -715,7 +719,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +731,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>instructor_rating</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Instructor Rating</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +777,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>course_rating</t>
+          <t>course_rating_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Course Rating</t>
+          <t>Course Rating 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,294 +800,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>instructor_rating</t>
+          <t>instructor_rating_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Instructor Rating</t>
+          <t>Instructor Rating 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>instructor_name_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Instructor Name</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>course_title_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>course_materials_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>course_structure_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Course Structure</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Teaching Effectiveness</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>course_rating_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Course Rating</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>department_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>instructor_rating_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Instructor Rating</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>course_title_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Course Title</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>course_materials_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>course_structure_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Course Structure</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Teaching Effectiveness</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +826,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,340 +854,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>teaching_effectiveness_choices</t>
+          <t>materials_provision_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>the_course_was_excellent_in_meeting_my_expectations.</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The course was excellent in meeting my expectations.</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>teaching_effectiveness_choices</t>
+          <t>materials_provision_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>the_course_was_good,_but_not_excellent_in_meeting_my_expectations.</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The course was good, but not excellent in meeting my expectations.</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>teaching_effectiveness_choices</t>
+          <t>materials_provision_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>the_course_was_neither_excellent_nor_poor_in_meeting_my_expectations.</t>
+          <t>partially</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The course was neither excellent nor poor in meeting my expectations.</t>
+          <t>Partially</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>teaching_effectiveness_choices</t>
+          <t>materials_provision_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>the_course_was_poor_in_meeting_my_expectations.</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The course was poor in meeting my expectations.</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>teaching_effectiveness_choices</t>
+          <t>course_structure_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>the_course_was_below_my_expectations.</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The course was below my expectations.</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>teaching_effectiveness_choices</t>
+          <t>course_structure_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>the_course_was_very_poor_in_meeting_my_expectations.</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The course was very poor in meeting my expectations.</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>teaching_effectiveness_choices</t>
+          <t>course_structure_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>the_course_was_the_worst_experience_i_had.</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The course was the worst experience I had.</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>course_materials_choices</t>
+          <t>course_structure_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>course_materials_choices</t>
+          <t>course_rating_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>course_materials_choices</t>
+          <t>course_rating_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>partially</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Partially</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>course_materials_choices</t>
+          <t>course_rating_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>course_structure_choices</t>
+          <t>instructor_impression_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>well</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Well</t>
+          <t>Very effective</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>course_structure_choices</t>
+          <t>instructor_impression_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>poorly</t>
+          <t>fairly_effective</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poorly</t>
+          <t>Fairly effective</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>course_structure_choices</t>
+          <t>instructor_impression_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>very_poorly</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Very poorly</t>
+          <t>Not very effective</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>course_structure_choices</t>
+          <t>instructor_impression_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>not_at_all_effective</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not at all effective</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>course_rating_choices</t>
+          <t>instructor_effectiveness_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Very effective</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>course_rating_choices</t>
+          <t>instructor_effectiveness_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>fairly_effective</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Fairly effective</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>course_rating_choices</t>
+          <t>instructor_effectiveness_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Not very effective</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>course_rating_choices</t>
+          <t>instructor_effectiveness_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>not_at_all_effective</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Not at all effective</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>course_rating_choices</t>
+          <t>instructor_rating_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1199,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1488,641 +1216,114 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>instructor_rating_choices</t>
+          <t>course_rating_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>instructor_rating_choices</t>
+          <t>course_rating_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>instructor_rating_choices</t>
+          <t>course_rating_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>course_materials_2_choices</t>
+          <t>instructor_rating_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Very good</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>course_materials_2_choices</t>
+          <t>instructor_rating_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>course_materials_2_choices</t>
+          <t>instructor_rating_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>course_materials_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>course_structure_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>very_good</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>course_structure_2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>course_structure_2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>course_structure_2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>very_effective</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Very effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>fairly_effective</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Fairly effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>not_very_effective</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Not very effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_2_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>not_at_all_effective</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Not at all effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>course_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>course_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>course_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>course_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>course_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>instructor_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>instructor_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>instructor_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>instructor_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>instructor_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>course_materials_3_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>very_good</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>course_materials_3_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>course_materials_3_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>course_materials_3_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>course_structure_3_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>very_good</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Very good</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>course_structure_3_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>course_structure_3_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>course_structure_3_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_3_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>very_effective</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Very effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_3_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>fairly_effective</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Fairly effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_3_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>not_very_effective</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Not very effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>teaching_effectiveness_3_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>not_at_all_effective</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Not at all effective</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
